--- a/All_strategies_monthly_percentages.xlsx
+++ b/All_strategies_monthly_percentages.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kk\PycharmProjects\Flex_web_service\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\daily reports\factsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16B0D50-5B6D-4150-8DF9-3899CD238A05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5C8F10-DE3D-49D5-8054-6A30455230B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28530" yWindow="720" windowWidth="27210" windowHeight="14955" tabRatio="702" xr2:uid="{CB8D1963-12D9-434A-9948-227E7F96E66F}"/>
+    <workbookView xWindow="-27570" yWindow="600" windowWidth="27210" windowHeight="14955" tabRatio="702" xr2:uid="{CB8D1963-12D9-434A-9948-227E7F96E66F}"/>
   </bookViews>
   <sheets>
     <sheet name="Monthly_returns" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="141">
   <si>
     <t>Date</t>
   </si>
@@ -386,6 +386,12 @@
     <t>UBS Total PnL</t>
   </si>
   <si>
+    <t>IB</t>
+  </si>
+  <si>
+    <t>TDIV</t>
+  </si>
+  <si>
     <t>Month</t>
   </si>
   <si>
@@ -428,10 +434,40 @@
     <t>Dec</t>
   </si>
   <si>
+    <t>LYP6</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>TR212</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>VWCE</t>
+  </si>
+  <si>
     <t>+0.98% (MTD)</t>
   </si>
   <si>
     <t>AI Equities</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Pnl_Alloc_%</t>
+  </si>
+  <si>
+    <t>Perf_on_capital</t>
+  </si>
+  <si>
+    <t>Perf_contr_%</t>
+  </si>
+  <si>
+    <t>Equities_CDNE_Euro_Hedged</t>
   </si>
 </sst>
 </file>
@@ -543,7 +579,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -588,6 +624,7 @@
     <xf numFmtId="10" fontId="0" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -964,7 +1001,7 @@
     <col min="26" max="27" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1011,7 +1048,7 @@
         <v>33</v>
       </c>
       <c r="P1" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="Q1" t="s">
         <v>47</v>
@@ -1023,10 +1060,31 @@
         <v>51</v>
       </c>
       <c r="T1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="U1" t="s">
+        <v>132</v>
+      </c>
+      <c r="V1" t="s">
+        <v>113</v>
+      </c>
+      <c r="W1" t="s">
+        <v>130</v>
+      </c>
+      <c r="X1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>43952</v>
       </c>
@@ -1037,7 +1095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>43983</v>
       </c>
@@ -1048,7 +1106,7 @@
         <v>1.1000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>44013</v>
       </c>
@@ -1059,7 +1117,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>44044</v>
       </c>
@@ -1070,7 +1128,7 @@
         <v>0.5071</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>44075</v>
       </c>
@@ -1081,7 +1139,7 @@
         <v>0.2225</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>44105</v>
       </c>
@@ -1092,7 +1150,7 @@
         <v>2.07E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>44136</v>
       </c>
@@ -1103,7 +1161,7 @@
         <v>4.8099999999999997E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>44166</v>
       </c>
@@ -1114,7 +1172,7 @@
         <v>0.36799999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>44197</v>
       </c>
@@ -1125,7 +1183,7 @@
         <v>5.5399999999999998E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>44228</v>
       </c>
@@ -1136,7 +1194,7 @@
         <v>0.1298</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>44256</v>
       </c>
@@ -1147,7 +1205,7 @@
         <v>-6.6799999999999998E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>44287</v>
       </c>
@@ -1158,7 +1216,7 @@
         <v>0.2326</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>44317</v>
       </c>
@@ -1181,7 +1239,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>44348</v>
       </c>
@@ -1204,7 +1262,7 @@
         <v>-1.89E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>44378</v>
       </c>
@@ -1617,8 +1675,14 @@
       <c r="Q33" s="10">
         <v>-2.7000000000000001E-3</v>
       </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="10">
+        <v>0</v>
+      </c>
       <c r="AD33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AE33">
         <v>2023</v>
@@ -1655,11 +1719,17 @@
       <c r="Q34" s="10">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="Y34" s="2"/>
-      <c r="Z34" s="2"/>
-      <c r="AA34" s="2"/>
+      <c r="Y34" s="2">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="Z34" s="2">
+        <v>6.7400000000000002E-2</v>
+      </c>
+      <c r="AA34" s="2">
+        <v>5.3100000000000001E-2</v>
+      </c>
       <c r="AD34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.25">
@@ -1684,14 +1754,20 @@
       <c r="Q35" s="10">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="Y35" s="2"/>
-      <c r="Z35" s="2"/>
-      <c r="AA35" s="2"/>
+      <c r="Y35" s="2">
+        <v>-1.18E-2</v>
+      </c>
+      <c r="Z35" s="2">
+        <v>1.89E-2</v>
+      </c>
+      <c r="AA35" s="2">
+        <v>6.4999999999999997E-3</v>
+      </c>
       <c r="AD35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AH35" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.25">
@@ -1716,14 +1792,20 @@
       <c r="Q36" s="10">
         <v>3.5200000000000002E-2</v>
       </c>
-      <c r="Y36" s="2"/>
-      <c r="Z36" s="2"/>
-      <c r="AA36" s="2"/>
+      <c r="Y36" s="2">
+        <v>-3.7199999999999997E-2</v>
+      </c>
+      <c r="Z36" s="2">
+        <v>-6.7999999999999996E-3</v>
+      </c>
+      <c r="AA36" s="2">
+        <v>4.1999999999999997E-3</v>
+      </c>
       <c r="AD36" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AH36" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.25">
@@ -1748,14 +1830,20 @@
       <c r="Q37" s="10">
         <v>-1.0800000000000001E-2</v>
       </c>
-      <c r="Y37" s="2"/>
-      <c r="Z37" s="2"/>
-      <c r="AA37" s="2"/>
+      <c r="Y37" s="2">
+        <v>3.85E-2</v>
+      </c>
+      <c r="Z37" s="2">
+        <v>2.5399999999999999E-2</v>
+      </c>
+      <c r="AA37" s="2">
+        <v>-6.1999999999999998E-3</v>
+      </c>
       <c r="AD37" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AH37" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.25">
@@ -1801,14 +1889,20 @@
       <c r="T38" s="10">
         <v>0</v>
       </c>
-      <c r="Y38" s="2"/>
-      <c r="Z38" s="2"/>
-      <c r="AA38" s="2"/>
+      <c r="Y38" s="2">
+        <v>-6.0400000000000002E-2</v>
+      </c>
+      <c r="Z38" s="2">
+        <v>-2.4799999999999999E-2</v>
+      </c>
+      <c r="AA38" s="2">
+        <v>2.4799999999999999E-2</v>
+      </c>
       <c r="AD38" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH38" t="s">
         <v>119</v>
-      </c>
-      <c r="AH38" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.25">
@@ -1857,14 +1951,20 @@
       <c r="T39" s="2">
         <v>2.63E-2</v>
       </c>
-      <c r="Y39" s="2"/>
-      <c r="Z39" s="2"/>
-      <c r="AA39" s="2"/>
+      <c r="Y39" s="2">
+        <v>4.9200000000000001E-2</v>
+      </c>
+      <c r="Z39" s="2">
+        <v>2.41E-2</v>
+      </c>
+      <c r="AA39" s="2">
+        <v>3.32E-2</v>
+      </c>
       <c r="AD39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AH39" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.25">
@@ -1919,14 +2019,20 @@
       <c r="T40" s="2">
         <v>1.9300000000000001E-2</v>
       </c>
-      <c r="Y40" s="2"/>
-      <c r="Z40" s="2"/>
-      <c r="AA40" s="2"/>
+      <c r="Y40" s="2">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="Z40" s="2">
+        <v>2.0199999999999999E-2</v>
+      </c>
+      <c r="AA40" s="2">
+        <v>1.8499999999999999E-2</v>
+      </c>
       <c r="AD40" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AH40" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.25">
@@ -1981,14 +2087,20 @@
       <c r="T41" s="2">
         <v>-2.0299999999999999E-2</v>
       </c>
-      <c r="Y41" s="2"/>
-      <c r="Z41" s="2"/>
-      <c r="AA41" s="2"/>
+      <c r="Y41" s="2">
+        <v>-3.2399999999999998E-2</v>
+      </c>
+      <c r="Z41" s="2">
+        <v>-2.4500000000000001E-2</v>
+      </c>
+      <c r="AA41" s="2">
+        <v>-1.52E-2</v>
+      </c>
       <c r="AD41" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AH41" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.25">
@@ -2043,14 +2155,20 @@
       <c r="T42" s="2">
         <v>-1.9099999999999999E-2</v>
       </c>
-      <c r="Y42" s="2"/>
-      <c r="Z42" s="2"/>
-      <c r="AA42" s="2"/>
+      <c r="Y42" s="2">
+        <v>-1.2200000000000001E-2</v>
+      </c>
+      <c r="Z42" s="2">
+        <v>-1.61E-2</v>
+      </c>
+      <c r="AA42" s="2">
+        <v>-1.8200000000000001E-2</v>
+      </c>
       <c r="AD42" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AH42" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.25">
@@ -2105,14 +2223,20 @@
       <c r="T43" s="2">
         <v>-3.3300000000000003E-2</v>
       </c>
-      <c r="Y43" s="2"/>
-      <c r="Z43" s="2"/>
-      <c r="AA43" s="2"/>
+      <c r="Y43" s="2">
+        <v>-4.0099999999999997E-2</v>
+      </c>
+      <c r="Z43" s="2">
+        <v>-3.6400000000000002E-2</v>
+      </c>
+      <c r="AA43" s="2">
+        <v>-3.5099999999999999E-2</v>
+      </c>
       <c r="AD43" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AH43" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.25">
@@ -2167,14 +2291,20 @@
       <c r="T44" s="2">
         <v>4.2500000000000003E-2</v>
       </c>
-      <c r="Y44" s="40"/>
-      <c r="Z44" s="40"/>
-      <c r="AA44" s="40"/>
+      <c r="Y44" s="40">
+        <v>7.8200000000000006E-2</v>
+      </c>
+      <c r="Z44" s="40">
+        <v>6.4199999999999993E-2</v>
+      </c>
+      <c r="AA44" s="40">
+        <v>6.2399999999999997E-2</v>
+      </c>
       <c r="AD44" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AH44" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.25">
@@ -2229,14 +2359,20 @@
       <c r="T45" s="2">
         <v>6.1199999999999997E-2</v>
       </c>
-      <c r="Y45" s="2"/>
-      <c r="Z45" s="2"/>
-      <c r="AA45" s="2"/>
+      <c r="Y45" s="2">
+        <v>6.2100000000000002E-2</v>
+      </c>
+      <c r="Z45" s="2">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="AA45" s="2">
+        <v>3.5200000000000002E-2</v>
+      </c>
       <c r="AD45" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="AH45" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.25">
@@ -2291,17 +2427,27 @@
       <c r="T46" s="2">
         <v>-1E-3</v>
       </c>
-      <c r="U46" s="10"/>
-      <c r="V46" s="10"/>
+      <c r="U46" s="10">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="V46" s="10">
+        <v>2.1498695165900417E-2</v>
+      </c>
       <c r="W46" s="10"/>
-      <c r="Y46" s="2"/>
-      <c r="Z46" s="2"/>
-      <c r="AA46" s="2"/>
+      <c r="Y46" s="2">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="Z46" s="2">
+        <v>1.43E-2</v>
+      </c>
+      <c r="AA46" s="2">
+        <v>2.1499999999999998E-2</v>
+      </c>
       <c r="AE46" s="2"/>
       <c r="AF46" s="2"/>
       <c r="AG46" s="2"/>
       <c r="AH46" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.25">
@@ -2356,12 +2502,22 @@
       <c r="T47" s="2">
         <v>2.2499999999999999E-2</v>
       </c>
-      <c r="U47" s="10"/>
-      <c r="V47" s="10"/>
+      <c r="U47" s="10">
+        <v>6.13E-2</v>
+      </c>
+      <c r="V47" s="10">
+        <v>6.1334845906598545E-2</v>
+      </c>
       <c r="W47" s="10"/>
-      <c r="Y47" s="2"/>
-      <c r="Z47" s="2"/>
-      <c r="AA47" s="2"/>
+      <c r="Y47" s="2">
+        <v>1.8499999999999999E-2</v>
+      </c>
+      <c r="Z47" s="2">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="AA47" s="2">
+        <v>4.8599999999999997E-2</v>
+      </c>
       <c r="AG47" s="2"/>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
@@ -2416,12 +2572,24 @@
       <c r="T48" s="2">
         <v>4.1500000000000002E-2</v>
       </c>
-      <c r="U48" s="10"/>
-      <c r="V48" s="10"/>
-      <c r="W48" s="10"/>
-      <c r="Y48" s="2"/>
-      <c r="Z48" s="2"/>
-      <c r="AA48" s="2"/>
+      <c r="U48" s="10">
+        <v>2.0301863022990974E-2</v>
+      </c>
+      <c r="V48" s="10">
+        <v>4.1967354724926631E-2</v>
+      </c>
+      <c r="W48" s="10">
+        <v>9.3115819647437981E-3</v>
+      </c>
+      <c r="Y48" s="2">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="Z48" s="2">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="AA48" s="2">
+        <v>3.4099999999999998E-2</v>
+      </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
@@ -2475,12 +2643,24 @@
       <c r="T49" s="2">
         <v>-2.5600000000000001E-2</v>
       </c>
-      <c r="U49" s="10"/>
-      <c r="V49" s="10"/>
-      <c r="W49" s="10"/>
-      <c r="Y49" s="2"/>
-      <c r="Z49" s="2"/>
-      <c r="AA49" s="2"/>
+      <c r="U49" s="10">
+        <v>-1.1668163224583417E-2</v>
+      </c>
+      <c r="V49" s="10">
+        <v>-1.7204689912238003E-2</v>
+      </c>
+      <c r="W49" s="10">
+        <v>-8.5718063798507771E-3</v>
+      </c>
+      <c r="Y49" s="2">
+        <v>-1.52E-2</v>
+      </c>
+      <c r="Z49" s="2">
+        <v>-8.2000000000000007E-3</v>
+      </c>
+      <c r="AA49" s="2">
+        <v>-1.54E-2</v>
+      </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
@@ -2534,12 +2714,24 @@
       <c r="T50" s="2">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="U50" s="10"/>
-      <c r="V50" s="10"/>
-      <c r="W50" s="10"/>
-      <c r="Y50" s="2"/>
-      <c r="Z50" s="2"/>
-      <c r="AA50" s="2"/>
+      <c r="U50" s="10">
+        <v>1.4117635182540056E-2</v>
+      </c>
+      <c r="V50" s="10">
+        <v>1.7152076080495959E-2</v>
+      </c>
+      <c r="W50" s="10">
+        <v>1.2435371374324378E-2</v>
+      </c>
+      <c r="Y50" s="2">
+        <v>3.2800000000000003E-2</v>
+      </c>
+      <c r="Z50" s="2">
+        <v>3.32E-2</v>
+      </c>
+      <c r="AA50" s="2">
+        <v>2.5499999999999998E-2</v>
+      </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
@@ -2593,12 +2785,24 @@
       <c r="T51" s="2">
         <v>8.4599999999999995E-2</v>
       </c>
-      <c r="U51" s="10"/>
-      <c r="V51" s="10"/>
-      <c r="W51" s="10"/>
-      <c r="Y51" s="2"/>
-      <c r="Z51" s="2"/>
-      <c r="AA51" s="2"/>
+      <c r="U51" s="10">
+        <v>2.3592988636689904E-2</v>
+      </c>
+      <c r="V51" s="10">
+        <v>3.1117378812241414E-2</v>
+      </c>
+      <c r="W51" s="10">
+        <v>1.9301885090646786E-2</v>
+      </c>
+      <c r="Y51" s="2">
+        <v>-1.41E-2</v>
+      </c>
+      <c r="Z51" s="2">
+        <v>-1.32E-2</v>
+      </c>
+      <c r="AA51" s="2">
+        <v>1.6199999999999999E-2</v>
+      </c>
       <c r="AG51" s="2"/>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
@@ -2653,12 +2857,24 @@
       <c r="T52" s="2">
         <v>-4.8500000000000001E-2</v>
       </c>
-      <c r="U52" s="10"/>
-      <c r="V52" s="10"/>
-      <c r="W52" s="10"/>
-      <c r="Y52" s="2"/>
-      <c r="Z52" s="2"/>
-      <c r="AA52" s="2"/>
+      <c r="U52" s="10">
+        <v>-6.3269533825585089E-3</v>
+      </c>
+      <c r="V52" s="10">
+        <v>-1.2782002939859538E-4</v>
+      </c>
+      <c r="W52" s="10">
+        <v>-9.9032533994042327E-3</v>
+      </c>
+      <c r="Y52" s="2">
+        <v>4.24E-2</v>
+      </c>
+      <c r="Z52" s="2">
+        <v>1.52E-2</v>
+      </c>
+      <c r="AA52" s="2">
+        <v>1.4800000000000001E-2</v>
+      </c>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
@@ -2712,12 +2928,24 @@
       <c r="T53" s="2">
         <v>2.41E-2</v>
       </c>
-      <c r="U53" s="10"/>
-      <c r="V53" s="10"/>
-      <c r="W53" s="10"/>
-      <c r="Y53" s="2"/>
-      <c r="Z53" s="2"/>
-      <c r="AA53" s="2"/>
+      <c r="U53" s="10">
+        <v>1.5442983862349102E-2</v>
+      </c>
+      <c r="V53" s="10">
+        <v>8.367188711428053E-3</v>
+      </c>
+      <c r="W53" s="10">
+        <v>2.0365104910492704E-2</v>
+      </c>
+      <c r="Y53" s="2">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="Z53" s="2">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="AA53" s="2">
+        <v>7.7000000000000002E-3</v>
+      </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
@@ -2771,13 +2999,25 @@
       <c r="T54" s="2">
         <v>-7.7000000000000002E-3</v>
       </c>
-      <c r="U54" s="2"/>
-      <c r="V54" s="2"/>
-      <c r="W54" s="2"/>
+      <c r="U54" s="2">
+        <v>1.6751706738268979E-2</v>
+      </c>
+      <c r="V54" s="2">
+        <v>1.7433693133382056E-2</v>
+      </c>
+      <c r="W54" s="2">
+        <v>1.6279330863365971E-2</v>
+      </c>
       <c r="X54" s="2"/>
-      <c r="Y54" s="2"/>
-      <c r="Z54" s="2"/>
-      <c r="AA54" s="2"/>
+      <c r="Y54" s="2">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="Z54" s="2">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="AA54" s="2">
+        <v>8.0999999999999996E-3</v>
+      </c>
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
@@ -2831,12 +3071,24 @@
       <c r="T55" s="2">
         <v>1.4800000000000001E-2</v>
       </c>
-      <c r="U55" s="10"/>
-      <c r="V55" s="10"/>
-      <c r="W55" s="10"/>
-      <c r="Y55" s="2"/>
-      <c r="Z55" s="2"/>
-      <c r="AA55" s="2"/>
+      <c r="U55" s="10">
+        <v>1.9164882744357126E-2</v>
+      </c>
+      <c r="V55" s="10">
+        <v>1.9182430757974434E-2</v>
+      </c>
+      <c r="W55" s="10">
+        <v>1.9152714358193768E-2</v>
+      </c>
+      <c r="Y55" s="2">
+        <v>-2.8799999999999999E-2</v>
+      </c>
+      <c r="Z55" s="2">
+        <v>-3.1199999999999999E-2</v>
+      </c>
+      <c r="AA55" s="2">
+        <v>-3.15E-2</v>
+      </c>
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
@@ -2890,12 +3142,24 @@
       <c r="T56" s="2">
         <v>6.4699999999999994E-2</v>
       </c>
-      <c r="U56" s="10"/>
-      <c r="V56" s="10"/>
-      <c r="W56" s="10"/>
-      <c r="Y56" s="40"/>
-      <c r="Z56" s="40"/>
-      <c r="AA56" s="40"/>
+      <c r="U56" s="10">
+        <v>2.5010645263201292E-2</v>
+      </c>
+      <c r="V56" s="10">
+        <v>4.2297471762124506E-2</v>
+      </c>
+      <c r="W56" s="10">
+        <v>1.3703921086013926E-2</v>
+      </c>
+      <c r="Y56" s="40">
+        <v>1.24E-2</v>
+      </c>
+      <c r="Z56" s="40">
+        <v>1.18E-2</v>
+      </c>
+      <c r="AA56" s="40">
+        <v>4.1200000000000001E-2</v>
+      </c>
     </row>
     <row r="57" spans="1:33" s="43" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="38">
@@ -2958,13 +3222,27 @@
       <c r="T57" s="40">
         <v>-3.04E-2</v>
       </c>
-      <c r="U57" s="41"/>
-      <c r="V57" s="41"/>
-      <c r="W57" s="41"/>
-      <c r="X57" s="42"/>
-      <c r="Y57" s="2"/>
-      <c r="Z57" s="2"/>
-      <c r="AA57" s="2"/>
+      <c r="U57" s="41">
+        <v>-2.628763632384068E-3</v>
+      </c>
+      <c r="V57" s="41">
+        <v>7.9428999916686394E-4</v>
+      </c>
+      <c r="W57" s="41">
+        <v>-5.4014882108597284E-3</v>
+      </c>
+      <c r="X57" s="42">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="2">
+        <v>-1.9400000000000001E-2</v>
+      </c>
+      <c r="Z57" s="2">
+        <v>-1.9599999999999999E-2</v>
+      </c>
+      <c r="AA57" s="2">
+        <v>1.5800000000000002E-2</v>
+      </c>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
@@ -3027,13 +3305,27 @@
       <c r="T58" s="2">
         <v>2.92E-2</v>
       </c>
-      <c r="U58" s="10"/>
-      <c r="V58" s="10"/>
-      <c r="W58" s="10"/>
-      <c r="X58" s="10"/>
-      <c r="Y58" s="2"/>
-      <c r="Z58" s="2"/>
-      <c r="AA58" s="2"/>
+      <c r="U58" s="10">
+        <v>2.1309665883882944E-2</v>
+      </c>
+      <c r="V58" s="10">
+        <v>1.5941733180075079E-2</v>
+      </c>
+      <c r="W58" s="10">
+        <v>2.6008007271143052E-2</v>
+      </c>
+      <c r="X58" s="10">
+        <v>4.6773767023666757E-3</v>
+      </c>
+      <c r="Y58" s="2">
+        <v>3.5200000000000002E-2</v>
+      </c>
+      <c r="Z58" s="2">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="AA58" s="2">
+        <v>4.2000000000000003E-2</v>
+      </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
@@ -3096,13 +3388,27 @@
       <c r="T59" s="2">
         <v>-5.67E-2</v>
       </c>
-      <c r="U59" s="10"/>
-      <c r="V59" s="10"/>
-      <c r="W59" s="10"/>
-      <c r="X59" s="10"/>
-      <c r="Y59" s="2"/>
-      <c r="Z59" s="2"/>
-      <c r="AA59" s="2"/>
+      <c r="U59" s="10">
+        <v>-6.5904401844062432E-3</v>
+      </c>
+      <c r="V59" s="10">
+        <v>6.0799593964455667E-4</v>
+      </c>
+      <c r="W59" s="10">
+        <v>-1.0432770418868031E-2</v>
+      </c>
+      <c r="X59" s="10">
+        <v>-1.6272891429741199E-2</v>
+      </c>
+      <c r="Y59" s="2">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="Z59" s="2">
+        <v>2.7E-2</v>
+      </c>
+      <c r="AA59" s="2">
+        <v>-2.1999999999999999E-2</v>
+      </c>
       <c r="AD59" s="2"/>
       <c r="AE59" s="2"/>
       <c r="AF59" s="2"/>
@@ -3168,13 +3474,27 @@
       <c r="T60" s="2">
         <v>-4.8800000000000003E-2</v>
       </c>
-      <c r="U60" s="10"/>
-      <c r="V60" s="10"/>
-      <c r="W60" s="10"/>
-      <c r="X60" s="10"/>
-      <c r="Y60" s="2"/>
-      <c r="Z60" s="2"/>
-      <c r="AA60" s="2"/>
+      <c r="U60" s="10">
+        <v>-5.635653613161562E-2</v>
+      </c>
+      <c r="V60" s="10">
+        <v>-6.622600535768064E-2</v>
+      </c>
+      <c r="W60" s="10">
+        <v>-4.9905806640504702E-2</v>
+      </c>
+      <c r="X60" s="10">
+        <v>-5.1719858372123562E-2</v>
+      </c>
+      <c r="Y60" s="2">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="Z60" s="2">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AA60" s="2">
+        <v>-7.1999999999999995E-2</v>
+      </c>
       <c r="AF60" s="2"/>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
@@ -3238,13 +3558,27 @@
       <c r="T61" s="2">
         <v>-1.2999999999999999E-3</v>
       </c>
-      <c r="U61" s="10"/>
-      <c r="V61" s="10"/>
-      <c r="W61" s="10"/>
-      <c r="X61" s="10"/>
-      <c r="Y61" s="2"/>
-      <c r="Z61" s="2"/>
-      <c r="AA61" s="2"/>
+      <c r="U61" s="10">
+        <v>-4.7698831581440837E-3</v>
+      </c>
+      <c r="V61" s="10">
+        <v>-4.1940393940937182E-2</v>
+      </c>
+      <c r="W61" s="10">
+        <v>5.4988345792645887E-3</v>
+      </c>
+      <c r="X61" s="10">
+        <v>-5.4008727163296077E-3</v>
+      </c>
+      <c r="Y61" s="2">
+        <v>1.5800000000000002E-2</v>
+      </c>
+      <c r="Z61" s="2">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="AA61" s="2">
+        <v>-3.9E-2</v>
+      </c>
       <c r="AF61" s="2"/>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
@@ -3308,13 +3642,27 @@
       <c r="T62" s="2">
         <v>2.9399999999999999E-2</v>
       </c>
-      <c r="U62" s="10"/>
-      <c r="V62" s="10"/>
-      <c r="W62" s="10"/>
-      <c r="X62" s="10"/>
-      <c r="Y62" s="2"/>
-      <c r="Z62" s="2"/>
-      <c r="AA62" s="2"/>
+      <c r="U62" s="10">
+        <v>3.5154436193413297E-2</v>
+      </c>
+      <c r="V62" s="10">
+        <v>5.5011074033606056E-2</v>
+      </c>
+      <c r="W62" s="10">
+        <v>2.5931223626595168E-2</v>
+      </c>
+      <c r="X62" s="10">
+        <v>6.5021631426906978E-3</v>
+      </c>
+      <c r="Y62" s="2">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="Z62" s="2">
+        <v>1.9199999999999998E-2</v>
+      </c>
+      <c r="AA62" s="2">
+        <v>6.0999999999999999E-2</v>
+      </c>
       <c r="AF62" s="2"/>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
@@ -3378,13 +3726,27 @@
       <c r="T63" s="2">
         <v>1.61E-2</v>
       </c>
-      <c r="U63" s="10"/>
-      <c r="V63" s="10"/>
-      <c r="W63" s="10"/>
-      <c r="X63" s="10"/>
-      <c r="Y63" s="2"/>
-      <c r="Z63" s="2"/>
-      <c r="AA63" s="2"/>
+      <c r="U63" s="10">
+        <v>1.3828056486068885E-2</v>
+      </c>
+      <c r="V63" s="10">
+        <v>1.0534671822971742E-2</v>
+      </c>
+      <c r="W63" s="10">
+        <v>1.8064809073637056E-2</v>
+      </c>
+      <c r="X63" s="10">
+        <v>1.6747875143858781E-3</v>
+      </c>
+      <c r="Y63" s="2">
+        <v>-1.5E-3</v>
+      </c>
+      <c r="Z63" s="2">
+        <v>-1.8E-3</v>
+      </c>
+      <c r="AA63" s="2">
+        <v>0.01</v>
+      </c>
       <c r="AD63" s="2"/>
       <c r="AE63" s="2"/>
       <c r="AF63" s="2"/>
@@ -3450,13 +3812,27 @@
       <c r="T64" s="2">
         <v>2.47E-2</v>
       </c>
-      <c r="U64" s="10"/>
-      <c r="V64" s="10"/>
-      <c r="W64" s="10"/>
-      <c r="X64" s="10"/>
-      <c r="Y64" s="2"/>
-      <c r="Z64" s="2"/>
-      <c r="AA64" s="2"/>
+      <c r="U64" s="10">
+        <v>2.1379981087303213E-2</v>
+      </c>
+      <c r="V64" s="10">
+        <v>3.7792710693531184E-2</v>
+      </c>
+      <c r="W64" s="10">
+        <v>1.0641867445539077E-2</v>
+      </c>
+      <c r="X64" s="10">
+        <v>1.7474948219577291E-2</v>
+      </c>
+      <c r="Y64" s="2">
+        <v>-1.1000000000000001E-3</v>
+      </c>
+      <c r="Z64" s="2">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="AA64" s="2">
+        <v>4.7E-2</v>
+      </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
@@ -3519,13 +3895,27 @@
       <c r="T65" s="2">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="U65" s="10"/>
-      <c r="V65" s="10"/>
-      <c r="W65" s="10"/>
-      <c r="X65" s="10"/>
-      <c r="Y65" s="2"/>
-      <c r="Z65" s="2"/>
-      <c r="AA65" s="2"/>
+      <c r="U65" s="10">
+        <v>1.4812695422699473E-2</v>
+      </c>
+      <c r="V65" s="10">
+        <v>-4.1637084763490595E-4</v>
+      </c>
+      <c r="W65" s="10">
+        <v>2.5413239368718088E-2</v>
+      </c>
+      <c r="X65" s="10">
+        <v>1.7814211957592807E-2</v>
+      </c>
+      <c r="Y65" s="2">
+        <v>4.7E-2</v>
+      </c>
+      <c r="Z65" s="2">
+        <v>4.58E-2</v>
+      </c>
+      <c r="AA65" s="2">
+        <v>-3.0000000000000001E-3</v>
+      </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
@@ -3588,13 +3978,27 @@
       <c r="T66" s="2">
         <v>2.8899999999999999E-2</v>
       </c>
-      <c r="U66" s="10"/>
-      <c r="V66" s="10"/>
-      <c r="W66" s="10"/>
-      <c r="X66" s="10"/>
-      <c r="Y66" s="2"/>
-      <c r="Z66" s="2"/>
-      <c r="AA66" s="2"/>
+      <c r="U66" s="10">
+        <v>1.3266691859663116E-2</v>
+      </c>
+      <c r="V66" s="10">
+        <v>2.3385223358521889E-2</v>
+      </c>
+      <c r="W66" s="10">
+        <v>3.0094742644525718E-2</v>
+      </c>
+      <c r="X66" s="10">
+        <v>-0.10853010648596328</v>
+      </c>
+      <c r="Y66" s="2">
+        <v>5.4999999999999997E-3</v>
+      </c>
+      <c r="Z66" s="2">
+        <v>4.1999999999999997E-3</v>
+      </c>
+      <c r="AA66" s="2">
+        <v>2.9000000000000001E-2</v>
+      </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
@@ -3657,13 +4061,27 @@
       <c r="T67" s="2">
         <v>1.09E-2</v>
       </c>
-      <c r="U67" s="10"/>
-      <c r="V67" s="10"/>
-      <c r="W67" s="10"/>
-      <c r="X67" s="10"/>
-      <c r="Y67" s="2"/>
-      <c r="Z67" s="2"/>
-      <c r="AA67" s="2"/>
+      <c r="U67" s="10">
+        <v>2.7686429415639369E-2</v>
+      </c>
+      <c r="V67" s="10">
+        <v>3.2165482116952138E-2</v>
+      </c>
+      <c r="W67" s="10">
+        <v>2.3208029468071434E-2</v>
+      </c>
+      <c r="X67" s="10">
+        <v>3.0800141163446648E-2</v>
+      </c>
+      <c r="Y67" s="2">
+        <v>4.7999999999999996E-3</v>
+      </c>
+      <c r="Z67" s="2">
+        <v>8.8000000000000005E-3</v>
+      </c>
+      <c r="AA67" s="2">
+        <v>4.3999999999999997E-2</v>
+      </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
@@ -3726,13 +4144,27 @@
       <c r="T68" s="2">
         <v>-6.1000000000000004E-3</v>
       </c>
-      <c r="U68" s="10"/>
-      <c r="V68" s="10"/>
-      <c r="W68" s="10"/>
-      <c r="X68" s="10"/>
-      <c r="Y68" s="2"/>
-      <c r="Z68" s="40"/>
-      <c r="AA68" s="40"/>
+      <c r="U68" s="10">
+        <v>-4.7777319835635712E-3</v>
+      </c>
+      <c r="V68" s="10">
+        <v>-6.1173520460267028E-4</v>
+      </c>
+      <c r="W68" s="10">
+        <v>-2.3446658851113966E-3</v>
+      </c>
+      <c r="X68" s="10">
+        <v>-1.7736690763483942E-2</v>
+      </c>
+      <c r="Y68" s="2">
+        <v>4.3799999999999999E-2</v>
+      </c>
+      <c r="Z68" s="40">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="AA68" s="40">
+        <v>-5.0000000000000001E-3</v>
+      </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
@@ -3795,13 +4227,27 @@
       <c r="T69" s="2">
         <v>-1.72E-2</v>
       </c>
-      <c r="U69" s="10"/>
-      <c r="V69" s="10"/>
-      <c r="W69" s="10"/>
-      <c r="X69" s="10"/>
-      <c r="Y69" s="2"/>
-      <c r="Z69" s="2"/>
-      <c r="AA69" s="2"/>
+      <c r="U69" s="10">
+        <v>9.1836553329897094E-3</v>
+      </c>
+      <c r="V69" s="10">
+        <v>9.5205815547585448E-3</v>
+      </c>
+      <c r="W69" s="10">
+        <v>9.6278887583234329E-3</v>
+      </c>
+      <c r="X69" s="10">
+        <v>7.5419733158235136E-3</v>
+      </c>
+      <c r="Y69" s="2">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="Z69" s="2">
+        <v>4.0099999999999997E-2</v>
+      </c>
+      <c r="AA69" s="2">
+        <v>4.0000000000000001E-3</v>
+      </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
@@ -3864,11 +4310,50 @@
       <c r="T70" s="2">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="U70" s="10"/>
-      <c r="V70" s="10"/>
-      <c r="W70" s="10"/>
-      <c r="X70" s="10"/>
-      <c r="Y70" s="2"/>
+      <c r="U70" s="10">
+        <v>1.3004451776915201E-2</v>
+      </c>
+      <c r="V70" s="10">
+        <v>2.0981263686428608E-2</v>
+      </c>
+      <c r="W70" s="10">
+        <v>5.1915696397584199E-3</v>
+      </c>
+      <c r="X70" s="10">
+        <v>1.8011776931070367E-2</v>
+      </c>
+      <c r="Y70" s="2">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="Z70" s="10">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="AA70" s="10">
+        <v>1.24E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46054</v>
+      </c>
+      <c r="N71" s="2">
+        <v>8.3000000000000001E-3</v>
+      </c>
+      <c r="O71" s="2">
+        <v>-2.5999999999999999E-3</v>
+      </c>
+      <c r="U71" s="10">
+        <v>9.1841849220155088E-3</v>
+      </c>
+      <c r="V71" s="10">
+        <v>1.2038554032173021E-2</v>
+      </c>
+      <c r="W71" s="10">
+        <v>6.088825214899618E-3</v>
+      </c>
+      <c r="X71" s="10">
+        <v>1.1374020887728431E-2</v>
+      </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="O72" s="2" t="s">
@@ -7965,15 +8450,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F74054D5-CB3D-46AE-A251-C5982D963EE2}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7986,8 +8474,23 @@
       <c r="D1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" t="s">
+        <v>138</v>
+      </c>
+      <c r="I1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>46022</v>
       </c>
@@ -8000,8 +8503,11 @@
       <c r="D2" s="7">
         <v>0.23454462300000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2">
+        <v>81249689.420000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>46022</v>
       </c>
@@ -8014,8 +8520,11 @@
       <c r="D3" s="7">
         <v>0.25540432800000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>88475796.480000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>46022</v>
       </c>
@@ -8028,8 +8537,11 @@
       <c r="D4" s="7">
         <v>0.29631911399999999</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>102649277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>46022</v>
       </c>
@@ -8042,8 +8554,11 @@
       <c r="D5" s="7">
         <v>0.153672053</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>53234248</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>46022</v>
       </c>
@@ -8056,8 +8571,11 @@
       <c r="D6" s="7">
         <v>4.5376728999999998E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>15719163</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>46022</v>
       </c>
@@ -8070,11 +8588,14 @@
       <c r="D7" s="7">
         <v>1.4683152999999999E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>5086459</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>45991</v>
       </c>
@@ -8087,8 +8608,11 @@
       <c r="D9">
         <v>0.35415268799999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>107018152.40000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>45991</v>
       </c>
@@ -8101,8 +8625,11 @@
       <c r="D10">
         <v>0.21312859300000001</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>88600129.079999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>45991</v>
       </c>
@@ -8115,8 +8642,11 @@
       <c r="D11">
         <v>0.21598367099999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>75275093.390000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>45991</v>
       </c>
@@ -8129,8 +8659,11 @@
       <c r="D12">
         <v>0.15154704399999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>53064064.140000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>45991</v>
       </c>
@@ -8143,8 +8676,11 @@
       <c r="D13">
         <v>5.0418042000000003E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>18120044.399999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>45991</v>
       </c>
@@ -8157,8 +8693,11 @@
       <c r="D14">
         <v>1.4769963000000001E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>5108229.12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>46053</v>
       </c>
@@ -8169,10 +8708,25 @@
         <v>32</v>
       </c>
       <c r="D16" s="15">
-        <v>0.238802768</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.23866168099999999</v>
+      </c>
+      <c r="E16">
+        <v>83346685.079999998</v>
+      </c>
+      <c r="F16" s="44">
+        <v>-207205.13</v>
+      </c>
+      <c r="G16" s="14">
+        <v>-6.9400000000000003E-2</v>
+      </c>
+      <c r="H16" s="14">
+        <v>-2.5000000000000001E-3</v>
+      </c>
+      <c r="I16">
+        <v>-5.6999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>46053</v>
       </c>
@@ -8183,10 +8737,25 @@
         <v>9</v>
       </c>
       <c r="D17" s="15">
-        <v>0.25170599199999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.25155728199999999</v>
+      </c>
+      <c r="E17">
+        <v>87850154.519999996</v>
+      </c>
+      <c r="F17" s="44">
+        <v>396503.23</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0.13270000000000001</v>
+      </c>
+      <c r="H17" s="14">
+        <v>4.4999999999999997E-3</v>
+      </c>
+      <c r="I17">
+        <v>1.09E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>46053</v>
       </c>
@@ -8197,10 +8766,25 @@
         <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>0.29327505100000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.29310178100000001</v>
+      </c>
+      <c r="E18">
+        <v>102358542.8</v>
+      </c>
+      <c r="F18" s="44">
+        <v>894933.21</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0.29949999999999999</v>
+      </c>
+      <c r="H18" s="14">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="I18">
+        <v>2.47E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>46053</v>
       </c>
@@ -8211,10 +8795,25 @@
         <v>11</v>
       </c>
       <c r="D19" s="15">
-        <v>0.15231340700000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.152346589</v>
+      </c>
+      <c r="E19">
+        <v>53203275.5</v>
+      </c>
+      <c r="F19">
+        <v>745432.5</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0.2495</v>
+      </c>
+      <c r="H19" s="14">
+        <v>1.4E-2</v>
+      </c>
+      <c r="I19">
+        <v>2.0799999999999998E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>46053</v>
       </c>
@@ -8225,10 +8824,25 @@
         <v>10</v>
       </c>
       <c r="D20" s="15">
-        <v>4.9408221000000002E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4.9379030999999997E-2</v>
+      </c>
+      <c r="E20">
+        <v>17244404.309999999</v>
+      </c>
+      <c r="F20">
+        <v>1257197.02</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0.42080000000000001</v>
+      </c>
+      <c r="H20" s="14">
+        <v>7.2900000000000006E-2</v>
+      </c>
+      <c r="I20">
+        <v>3.47E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>46053</v>
       </c>
@@ -8239,8 +8853,27 @@
         <v>12</v>
       </c>
       <c r="D21" s="15">
-        <v>1.4494561E-2</v>
-      </c>
+        <v>1.4953637000000001E-2</v>
+      </c>
+      <c r="E21">
+        <v>5222187.6100000003</v>
+      </c>
+      <c r="F21">
+        <v>-99079.7</v>
+      </c>
+      <c r="G21" s="14">
+        <v>-3.32E-2</v>
+      </c>
+      <c r="H21" s="14">
+        <v>-1.9E-2</v>
+      </c>
+      <c r="I21">
+        <v>-2.7E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="D22" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/All_strategies_monthly_percentages.xlsx
+++ b/All_strategies_monthly_percentages.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\daily reports\factsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5C8F10-DE3D-49D5-8054-6A30455230B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E341A113-6C2D-45F9-BD78-BE2E97F878A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27570" yWindow="600" windowWidth="27210" windowHeight="14955" tabRatio="702" xr2:uid="{CB8D1963-12D9-434A-9948-227E7F96E66F}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="141">
   <si>
     <t>Date</t>
   </si>
@@ -4299,7 +4299,7 @@
         <v>1.46E-2</v>
       </c>
       <c r="Q70" s="2">
-        <v>-1.4800000000000001E-2</v>
+        <v>-7.9000000000000008E-3</v>
       </c>
       <c r="R70" s="10">
         <v>0.01</v>
@@ -4336,11 +4336,32 @@
       <c r="A71" s="1">
         <v>46054</v>
       </c>
+      <c r="B71" s="2">
+        <v>-2.1700000000000001E-2</v>
+      </c>
+      <c r="C71" s="2">
+        <v>-0.1205</v>
+      </c>
+      <c r="D71" s="2">
+        <v>-0.1414</v>
+      </c>
+      <c r="E71" s="2">
+        <v>-0.14940000000000001</v>
+      </c>
+      <c r="F71" s="2">
+        <v>-0.1981</v>
+      </c>
+      <c r="G71" s="2">
+        <v>1.6799999999999999E-2</v>
+      </c>
       <c r="N71" s="2">
         <v>8.3000000000000001E-3</v>
       </c>
       <c r="O71" s="2">
         <v>-2.5999999999999999E-3</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>-7.4999999999999997E-3</v>
       </c>
       <c r="U71" s="10">
         <v>9.1841849220155088E-3</v>
@@ -10693,7 +10714,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0743A309-C66E-411C-B223-F69457EC1277}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -10995,6 +11016,146 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11002,7 +11163,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790B04E2-D146-4E1A-A626-8B9AE1AB3B4E}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -11304,6 +11465,146 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B31" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="5">
+        <v>46081</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/All_strategies_monthly_percentages.xlsx
+++ b/All_strategies_monthly_percentages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\daily reports\factsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C504A9-9574-4B44-B38E-E30DCE684F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3AE405-41A2-45C4-B828-015BC77CEFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1695" windowWidth="24735" windowHeight="13425" tabRatio="775" xr2:uid="{CB8D1963-12D9-434A-9948-227E7F96E66F}"/>
+    <workbookView xWindow="-135" yWindow="16350" windowWidth="29040" windowHeight="16155" tabRatio="775" xr2:uid="{CB8D1963-12D9-434A-9948-227E7F96E66F}"/>
   </bookViews>
   <sheets>
     <sheet name="Monthly_returns" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="134">
   <si>
     <t>Date</t>
   </si>
@@ -439,6 +439,15 @@
   <si>
     <t>Copper</t>
   </si>
+  <si>
+    <t>BNKE</t>
+  </si>
+  <si>
+    <t>IS3S</t>
+  </si>
+  <si>
+    <t>XAIX</t>
+  </si>
 </sst>
 </file>
 
@@ -557,7 +566,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -604,15 +613,37 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -963,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBFACDC0-0EFE-4FC1-9DD2-E578A7ECBA25}">
-  <dimension ref="A1:AH72"/>
+  <dimension ref="A1:AH73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
@@ -982,9 +1013,10 @@
     <col min="20" max="20" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="16.28515625" customWidth="1"/>
     <col min="27" max="28" width="9.140625" style="10"/>
+    <col min="30" max="30" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1072,8 +1104,17 @@
       <c r="AC1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AD1" t="s">
+        <v>131</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>43952</v>
       </c>
@@ -1084,7 +1125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>43983</v>
       </c>
@@ -1095,7 +1136,7 @@
         <v>1.1000000000000001E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>44013</v>
       </c>
@@ -1106,7 +1147,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>44044</v>
       </c>
@@ -1117,7 +1158,7 @@
         <v>0.5071</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>44075</v>
       </c>
@@ -1128,7 +1169,7 @@
         <v>0.2225</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>44105</v>
       </c>
@@ -1139,7 +1180,7 @@
         <v>2.07E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>44136</v>
       </c>
@@ -1150,7 +1191,7 @@
         <v>4.8099999999999997E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>44166</v>
       </c>
@@ -1161,7 +1202,7 @@
         <v>0.36799999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>44197</v>
       </c>
@@ -1172,7 +1213,7 @@
         <v>5.5399999999999998E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>44228</v>
       </c>
@@ -1183,7 +1224,7 @@
         <v>0.1298</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>44256</v>
       </c>
@@ -1194,7 +1235,7 @@
         <v>-6.6799999999999998E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>44287</v>
       </c>
@@ -1205,7 +1246,7 @@
         <v>0.2326</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>44317</v>
       </c>
@@ -1228,7 +1269,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>44348</v>
       </c>
@@ -1251,7 +1292,7 @@
         <v>-1.89E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>44378</v>
       </c>
@@ -3744,7 +3785,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>45870</v>
       </c>
@@ -3828,7 +3869,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>45901</v>
       </c>
@@ -3912,7 +3953,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>45931</v>
       </c>
@@ -3996,7 +4037,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>45962</v>
       </c>
@@ -4080,93 +4121,93 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
+    <row r="69" spans="1:32" s="49" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="28">
         <v>45992</v>
       </c>
-      <c r="B69" s="3">
+      <c r="B69" s="33">
         <v>-8.6E-3</v>
       </c>
-      <c r="C69" s="2">
+      <c r="C69" s="47">
         <v>-3.2500000000000001E-2</v>
       </c>
-      <c r="D69" s="2">
+      <c r="D69" s="47">
         <v>2.2800000000000001E-2</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E69" s="47">
         <v>-2.9700000000000001E-2</v>
       </c>
-      <c r="F69" s="2">
+      <c r="F69" s="47">
         <v>-6.4999999999999997E-3</v>
       </c>
-      <c r="G69" s="2">
+      <c r="G69" s="47">
         <v>-2.6800000000000001E-3</v>
       </c>
-      <c r="H69" s="2">
+      <c r="H69" s="47">
         <v>2.75E-2</v>
       </c>
-      <c r="I69" s="2">
+      <c r="I69" s="47">
         <v>-2.1000000000000001E-2</v>
       </c>
-      <c r="J69" s="2">
+      <c r="J69" s="47">
         <v>-1.72E-2</v>
       </c>
-      <c r="K69" s="2">
+      <c r="K69" s="47">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="L69" s="2">
+      <c r="L69" s="47">
         <v>1.03E-2</v>
       </c>
-      <c r="M69" s="2">
+      <c r="M69" s="47">
         <v>-1.1000000000000001E-3</v>
       </c>
-      <c r="N69" s="2">
+      <c r="N69" s="47">
         <v>-2.0999999999999999E-3</v>
       </c>
-      <c r="O69" s="2">
+      <c r="O69" s="47">
         <v>-3.8999999999999998E-3</v>
       </c>
-      <c r="P69" s="2">
+      <c r="P69" s="47">
         <v>-8.8000000000000005E-3</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="Q69" s="47">
         <v>-1.2800000000000001E-2</v>
       </c>
-      <c r="R69" s="10">
+      <c r="R69" s="48">
         <v>-1.5599999999999999E-2</v>
       </c>
-      <c r="S69" s="10">
+      <c r="S69" s="48">
         <v>0</v>
       </c>
-      <c r="T69" s="2">
+      <c r="T69" s="47">
         <v>-2.1000000000000001E-2</v>
       </c>
-      <c r="U69" s="2">
+      <c r="U69" s="47">
         <v>-1.72E-2</v>
       </c>
-      <c r="V69" s="10">
+      <c r="V69" s="48">
         <v>9.1836553329897094E-3</v>
       </c>
-      <c r="W69" s="10">
+      <c r="W69" s="48">
         <v>9.5205815547585448E-3</v>
       </c>
-      <c r="X69" s="10">
+      <c r="X69" s="48">
         <v>9.6278887583234329E-3</v>
       </c>
-      <c r="Y69" s="10">
+      <c r="Y69" s="48">
         <v>7.5419733158235136E-3</v>
       </c>
-      <c r="Z69" s="2">
+      <c r="Z69" s="47">
         <v>4.4200000000000003E-2</v>
       </c>
-      <c r="AA69" s="2">
+      <c r="AA69" s="47">
         <v>4.0099999999999997E-2</v>
       </c>
-      <c r="AB69" s="2">
+      <c r="AB69" s="47">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46023</v>
       </c>
@@ -4251,8 +4292,20 @@
       <c r="AB70" s="10">
         <v>1.24E-2</v>
       </c>
-    </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC70" s="2">
+        <v>0.1399</v>
+      </c>
+      <c r="AD70" s="2">
+        <v>4.5600000000000002E-2</v>
+      </c>
+      <c r="AE70" s="2">
+        <v>5.4199999999999998E-2</v>
+      </c>
+      <c r="AF70" s="2">
+        <v>4.1999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46054</v>
       </c>
@@ -4331,9 +4384,20 @@
       <c r="AB71" s="10">
         <v>2.4E-2</v>
       </c>
-      <c r="AD71" s="48"/>
-    </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AC71" s="2">
+        <v>5.4300000000000001E-2</v>
+      </c>
+      <c r="AD71" s="50">
+        <v>-2.5999999999999999E-2</v>
+      </c>
+      <c r="AE71" s="2">
+        <v>4.6300000000000001E-2</v>
+      </c>
+      <c r="AF71" s="2">
+        <v>-1.55E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46082</v>
       </c>
@@ -4413,15 +4477,115 @@
         <v>-5.7000000000000002E-2</v>
       </c>
       <c r="AC72" s="10">
-        <v>-9.5000000000000001E-2</v>
+        <v>-9.4E-2</v>
+      </c>
+      <c r="AD72" s="10">
+        <v>-0.109</v>
+      </c>
+      <c r="AE72" s="2">
+        <v>-5.2999999999999999E-2</v>
+      </c>
+      <c r="AF72" s="2">
+        <v>-4.9299999999999997E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B73" s="2">
+        <v>-1.37E-2</v>
+      </c>
+      <c r="C73" s="2">
+        <v>0.1203</v>
+      </c>
+      <c r="D73" s="2">
+        <v>3.8399999999999997E-2</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0.1187</v>
+      </c>
+      <c r="F73" s="2">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="G73" s="2">
+        <v>1.8509999999999999E-2</v>
+      </c>
+      <c r="H73" s="2">
+        <v>-3.5000000000000001E-3</v>
+      </c>
+      <c r="I73" s="2">
+        <v>6.3799999999999996E-2</v>
+      </c>
+      <c r="J73" s="2">
+        <v>6.9900000000000004E-2</v>
+      </c>
+      <c r="M73" s="2">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="N73" s="2">
+        <v>2.07E-2</v>
+      </c>
+      <c r="O73" s="2">
+        <v>4.4000000000000003E-3</v>
+      </c>
+      <c r="P73" s="2">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>5.7200000000000001E-2</v>
+      </c>
+      <c r="S73" s="2">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="V73" s="2">
+        <v>6.8743493978708478E-2</v>
+      </c>
+      <c r="W73" s="2">
+        <v>6.9412711023820212E-2</v>
+      </c>
+      <c r="X73" s="2">
+        <v>5.9275521405049394E-2</v>
+      </c>
+      <c r="Y73" s="2">
+        <v>2.4509061336437495E-2</v>
+      </c>
+      <c r="Z73" s="2">
+        <v>1.17E-2</v>
+      </c>
+      <c r="AA73" s="10">
+        <v>5.6599999999999998E-2</v>
+      </c>
+      <c r="AB73" s="10">
+        <v>7.7799999999999994E-2</v>
+      </c>
+      <c r="AC73" s="2">
+        <v>-1.6400000000000001E-2</v>
+      </c>
+      <c r="AD73" s="10">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="AE73" s="2">
+        <v>0.1147</v>
+      </c>
+      <c r="AF73" s="2">
+        <v>0.16550000000000001</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AC1 V1:AB1048576 AC72">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="V1:AB1048576 AC72 AD72:AD73 AC1:AF1">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC34:AF73">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8516,7 +8680,7 @@
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.5703125" style="6" customWidth="1"/>
@@ -9296,11 +9460,185 @@
         <v>-2.7999999999999998E-4</v>
       </c>
     </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="14">
+        <v>0.22444</v>
+      </c>
+      <c r="E37">
+        <v>79186974</v>
+      </c>
+      <c r="F37" s="44">
+        <v>128177.08</v>
+      </c>
+      <c r="G37" s="7">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="H37" s="7">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="I37" s="14">
+        <v>3.4000000000000002E-4</v>
+      </c>
+      <c r="J37" s="6">
+        <v>550000</v>
+      </c>
+    </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J38" s="46"/>
+      <c r="A38" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="14">
+        <v>0.24356</v>
+      </c>
+      <c r="E38">
+        <v>85931359.790000007</v>
+      </c>
+      <c r="F38" s="44">
+        <v>-104473.4</v>
+      </c>
+      <c r="G38" s="7">
+        <v>-1.4E-2</v>
+      </c>
+      <c r="H38" s="7">
+        <v>-1.1999999999999999E-3</v>
+      </c>
+      <c r="I38" s="14">
+        <v>-2.7999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B39" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="14">
+        <v>0.29881000000000002</v>
+      </c>
+      <c r="E39">
+        <v>105426651.09999999</v>
+      </c>
+      <c r="F39" s="44">
+        <v>6122363</v>
+      </c>
+      <c r="G39" s="7">
+        <v>0.81899999999999995</v>
+      </c>
+      <c r="H39" s="7">
+        <v>5.8099999999999999E-2</v>
+      </c>
+      <c r="I39" s="14">
+        <v>1.6379999999999999E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="14">
+        <v>0.16578000000000001</v>
+      </c>
+      <c r="E40">
+        <v>58490475.439999998</v>
+      </c>
+      <c r="F40">
+        <v>424065.47</v>
+      </c>
+      <c r="G40" s="7">
+        <v>5.67E-2</v>
+      </c>
+      <c r="H40" s="7">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="I40" s="14">
+        <v>1.1299999999999999E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" t="s">
+        <v>10</v>
+      </c>
+      <c r="D41" s="14">
+        <v>5.2760000000000001E-2</v>
+      </c>
+      <c r="E41">
+        <v>18616474.25</v>
+      </c>
+      <c r="F41">
+        <v>1058218.1000000001</v>
+      </c>
+      <c r="G41" s="7">
+        <v>0.1416</v>
+      </c>
+      <c r="H41" s="7">
+        <v>5.6800000000000003E-2</v>
+      </c>
+      <c r="I41" s="14">
+        <v>2.8300000000000001E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="14">
+        <v>1.465E-2</v>
+      </c>
+      <c r="E42">
+        <v>5168125</v>
+      </c>
+      <c r="F42">
+        <v>-153142.15</v>
+      </c>
+      <c r="G42" s="7">
+        <v>-2.0500000000000001E-2</v>
+      </c>
+      <c r="H42" s="7">
+        <v>-2.9600000000000001E-2</v>
+      </c>
+      <c r="I42" s="14">
+        <v>-4.0999999999999999E-4</v>
+      </c>
     </row>
     <row r="57" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J57" s="47"/>
+      <c r="J57" s="46"/>
     </row>
     <row r="70" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J70" s="6">
@@ -9320,7 +9658,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95280BB3-3272-4D81-AF65-A7CD0438F538}">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -10162,6 +10500,90 @@
         <v>-2.7999999999999998E-4</v>
       </c>
     </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B82" t="s">
+        <v>13</v>
+      </c>
+      <c r="C82" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" s="14">
+        <v>3.4000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B83" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="14">
+        <v>-2.7999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B84" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" t="s">
+        <v>3</v>
+      </c>
+      <c r="D84" s="14">
+        <v>1.6379999999999999E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B85" t="s">
+        <v>13</v>
+      </c>
+      <c r="C85" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="14">
+        <v>1.1299999999999999E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B86" t="s">
+        <v>13</v>
+      </c>
+      <c r="C86" t="s">
+        <v>10</v>
+      </c>
+      <c r="D86" s="14">
+        <v>2.8300000000000001E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B87" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" t="s">
+        <v>12</v>
+      </c>
+      <c r="D87" s="14">
+        <v>-4.0999999999999999E-4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10169,7 +10591,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64B1EC6F-1F6B-4301-B283-6E401D9A2BD8}">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -10681,6 +11103,146 @@
         <v>0.1215</v>
       </c>
     </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45">
+        <v>4.9344811000000002E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D46">
+        <v>6.24758E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47">
+        <v>0.19807730200000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48">
+        <v>0.34826997399999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50">
+        <v>4.0635813999999999E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51">
+        <v>4.5541528999999997E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D52">
+        <v>4.9424112999999999E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53">
+        <v>0.15223852099999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B54" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54">
+        <v>0.115843179</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A22:D30">
     <sortCondition ref="C22:C30"/>
@@ -10691,7 +11253,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA51606F-1083-4B7B-81B9-25B5BA84FD21}">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -11439,6 +12001,118 @@
       </c>
       <c r="D65">
         <v>2.0256060000000001E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67">
+        <v>0.77908846700000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D68">
+        <v>0.16446756100000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D69">
+        <v>5.5993312000000003E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70">
+        <v>4.5066000000000003E-4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B72" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72">
+        <v>0.77908846700000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B73" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73">
+        <v>0.16446756100000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74">
+        <v>5.5993312000000003E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B75" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D75">
+        <v>4.5066000000000003E-4</v>
       </c>
     </row>
   </sheetData>
@@ -11650,7 +12324,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C86F5A44-8B26-4377-AC01-E2E6B8EEC9CB}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -11896,6 +12570,62 @@
         <v>0.59308245400000004</v>
       </c>
     </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="45">
+        <v>46142</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23">
+        <v>0.186648763</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="45">
+        <v>46142</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24">
+        <v>0.214578451</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="45">
+        <v>46142</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>126</v>
+      </c>
+      <c r="D25">
+        <v>5.0885540000000003E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="45">
+        <v>46142</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26">
+        <v>0.59368423199999998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11903,7 +12633,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0743A309-C66E-411C-B223-F69457EC1277}">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -12345,6 +13075,286 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D38" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B44" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B45" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B49" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B50" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B51" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D52" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D53" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B54" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B55" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B56" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D56" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12352,7 +13362,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{790B04E2-D146-4E1A-A626-8B9AE1AB3B4E}">
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -12934,6 +13944,146 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B48" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B50" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D50" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D51" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B52" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D52" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D53" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>46142</v>
+      </c>
+      <c r="B55" t="s">
+        <v>47</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D55" s="9">
+        <v>0.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
